--- a/outputs/109-21.xlsx
+++ b/outputs/109-21.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="23">
   <si>
     <t xml:space="preserve">Total points</t>
   </si>
@@ -31,7 +31,13 @@
     <t xml:space="preserve">x</t>
   </si>
   <si>
+    <t xml:space="preserve">Y</t>
+  </si>
+  <si>
     <t xml:space="preserve">Noah</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N</t>
   </si>
   <si>
     <t xml:space="preserve">Oliver</t>
@@ -178,23 +184,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -484,14 +490,13 @@
       <c r="X5" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Z5" s="1" t="str">
-        <f aca="false">IF(K5=MAX(K5:K6),"Y","N")</f>
-        <v>Y</v>
+      <c r="Z5" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>2</v>
@@ -553,9 +558,8 @@
       <c r="X6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Z6" s="1" t="str">
-        <f aca="false">IF(K6=MAX(K5:K6),"Y","N")</f>
-        <v>N</v>
+      <c r="Z6" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -569,7 +573,7 @@
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B10" s="1" t="n">
         <v>3</v>
@@ -634,14 +638,13 @@
       <c r="X10" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Z10" s="1" t="str">
-        <f aca="false">IF(K10=MAX(K10:K11),"Y","N")</f>
-        <v>Y</v>
+      <c r="Z10" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B11" s="1" t="n">
         <v>3</v>
@@ -703,9 +706,8 @@
       <c r="X11" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Z11" s="1" t="str">
-        <f aca="false">IF(K11=MAX(K10:K11),"Y","N")</f>
-        <v>N</v>
+      <c r="Z11" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -719,7 +721,7 @@
     </row>
     <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B15" s="1" t="n">
         <v>4</v>
@@ -784,14 +786,13 @@
       <c r="X15" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Z15" s="1" t="str">
-        <f aca="false">IF(K15=MAX(K15:K16),"Y","N")</f>
-        <v>Y</v>
+      <c r="Z15" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B16" s="1" t="n">
         <v>4</v>
@@ -853,9 +854,8 @@
       <c r="X16" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Z16" s="1" t="str">
-        <f aca="false">IF(K16=MAX(K15:K16),"Y","N")</f>
-        <v>N</v>
+      <c r="Z16" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -869,7 +869,7 @@
     </row>
     <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B20" s="1" t="n">
         <v>5</v>
@@ -934,14 +934,13 @@
       <c r="X20" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="Z20" s="1" t="str">
-        <f aca="false">IF(K20=MAX(K20:K21),"Y","N")</f>
-        <v>Y</v>
+      <c r="Z20" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B21" s="1" t="n">
         <v>5</v>
@@ -1003,9 +1002,8 @@
       <c r="X21" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Z21" s="1" t="str">
-        <f aca="false">IF(K21=MAX(K20:K21),"Y","N")</f>
-        <v>N</v>
+      <c r="Z21" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1019,7 +1017,7 @@
     </row>
     <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B25" s="1" t="n">
         <v>7</v>
@@ -1084,14 +1082,13 @@
       <c r="X25" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Z25" s="1" t="str">
-        <f aca="false">IF(K25=MAX(K25:K27),"Y","N")</f>
-        <v>Y</v>
+      <c r="Z25" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B26" s="1" t="n">
         <v>7</v>
@@ -1153,14 +1150,13 @@
       <c r="X26" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Z26" s="1" t="str">
-        <f aca="false">IF(K26=MAX(K25:K27),"Y","N")</f>
-        <v>N</v>
+      <c r="Z26" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B27" s="1" t="n">
         <v>7</v>
@@ -1222,9 +1218,8 @@
       <c r="X27" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="Z27" s="1" t="str">
-        <f aca="false">IF(K27=MAX(K25:K27),"Y","N")</f>
-        <v>N</v>
+      <c r="Z27" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1238,7 +1233,7 @@
     </row>
     <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B31" s="1" t="n">
         <v>8</v>
@@ -1303,14 +1298,13 @@
       <c r="X31" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Z31" s="1" t="str">
-        <f aca="false">IF(K31=MAX(K31:K33),"Y","N")</f>
-        <v>Y</v>
+      <c r="Z31" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B32" s="1" t="n">
         <v>8</v>
@@ -1372,14 +1366,13 @@
       <c r="X32" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="Z32" s="1" t="str">
-        <f aca="false">IF(K32=MAX(K31:K33),"Y","N")</f>
-        <v>Y</v>
+      <c r="Z32" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B33" s="1" t="n">
         <v>8</v>
@@ -1441,9 +1434,8 @@
       <c r="X33" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Z33" s="1" t="str">
-        <f aca="false">IF(K33=MAX(K31:K33),"Y","N")</f>
-        <v>Y</v>
+      <c r="Z33" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1457,7 +1449,7 @@
     </row>
     <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B37" s="1" t="n">
         <v>9</v>
@@ -1519,9 +1511,8 @@
       <c r="X37" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Z37" s="1" t="str">
-        <f aca="false">IF(K37=MAX(K37),"Y","N")</f>
-        <v>Y</v>
+      <c r="Z37" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1532,7 +1523,7 @@
     </row>
     <row r="40" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B40" s="1" t="n">
         <v>2</v>
@@ -1597,14 +1588,13 @@
       <c r="X40" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Z40" s="1" t="str">
-        <f aca="false">IF(K40=MAX(K40:K43),"Y","N")</f>
-        <v>Y</v>
+      <c r="Z40" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B41" s="1" t="n">
         <v>2</v>
@@ -1669,14 +1659,13 @@
       <c r="X41" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="Z41" s="1" t="str">
-        <f aca="false">IF(K41=MAX(K40:K43),"Y","N")</f>
-        <v>Y</v>
+      <c r="Z41" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B42" s="1" t="n">
         <v>2</v>
@@ -1738,14 +1727,13 @@
       <c r="X42" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="Z42" s="1" t="str">
-        <f aca="false">IF(K42=MAX(K40:K43),"Y","N")</f>
-        <v>N</v>
+      <c r="Z42" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B43" s="1" t="n">
         <v>2</v>
@@ -1807,9 +1795,8 @@
       <c r="X43" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="Z43" s="1" t="str">
-        <f aca="false">IF(K43=MAX(K40:K43),"Y","N")</f>
-        <v>N</v>
+      <c r="Z43" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
